--- a/survey_templates/037_utility_service_reliability_assessment_form--survey_templates.xlsx
+++ b/survey_templates/037_utility_service_reliability_assessment_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_4,_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 4, 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_none,_'value':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': None, 'value': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Daily', 'value': 'daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly', 'value': 'weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Never', 'value': 'never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'high_winds',_'value':_'high_winds'}</t>
+          <t>high_winds</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'High winds', 'value': 'high_winds'}</t>
+          <t>High winds</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'lightning',_'value':_'lightning'}</t>
+          <t>lightning</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Lightning', 'value': 'lightning'}</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)',_'value':_'other'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)', 'value': 'other'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_completed',_'value':_'not_completed'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not completed', 'value': 'not_completed'}</t>
+          <t>Not completed</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'1-5',_'value':_'1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': '1-5', 'value': '1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'6-10',_'value':_'6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': '6-10', 'value': '6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_5',_'value':_'more_than_5'}</t>
+          <t>more_than_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'More than 5', 'value': 'more_than_5'}</t>
+          <t>More than 5</t>
         </is>
       </c>
     </row>
